--- a/project/demo website .xlsx
+++ b/project/demo website .xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RUCHIT THAKOR\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4f57d8c88bda9653/Pictures/Documents/GitHub/om-testing/project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28D5B7BF-429F-42A1-9719-D3CD60B9A77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{28D5B7BF-429F-42A1-9719-D3CD60B9A77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64D2528D-1656-426C-8A14-0D299660A9F1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{25798F5A-7913-42B7-83C9-F1F5A6789213}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{25798F5A-7913-42B7-83C9-F1F5A6789213}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="hlr" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -374,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -388,9 +389,6 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -726,14 +724,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAAD72FB-2C0D-408E-9545-D8EA891EBC45}">
   <dimension ref="A1:C137"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="2" max="2" width="45.21875" customWidth="1"/>
-    <col min="3" max="3" width="113.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="45.28515625" customWidth="1"/>
+    <col min="3" max="3" width="113.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="45.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -744,14 +742,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -762,7 +760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -773,7 +771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -784,7 +782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>100</v>
       </c>
@@ -795,7 +793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>200</v>
       </c>
@@ -806,7 +804,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>300</v>
       </c>
@@ -817,7 +815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>301</v>
       </c>
@@ -828,7 +826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>302</v>
       </c>
@@ -839,7 +837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>303</v>
       </c>
@@ -850,7 +848,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>304</v>
       </c>
@@ -861,7 +859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>305</v>
       </c>
@@ -872,7 +870,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>306</v>
       </c>
@@ -883,7 +881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>307</v>
       </c>
@@ -894,7 +892,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>308</v>
       </c>
@@ -905,7 +903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>309</v>
       </c>
@@ -916,7 +914,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>310</v>
       </c>
@@ -927,7 +925,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>311</v>
       </c>
@@ -938,13 +936,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>312</v>
       </c>
@@ -955,7 +953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>313</v>
       </c>
@@ -966,7 +964,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>314</v>
       </c>
@@ -977,7 +975,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>315</v>
       </c>
@@ -988,7 +986,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>316</v>
       </c>
@@ -999,7 +997,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>317</v>
       </c>
@@ -1010,7 +1008,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>318</v>
       </c>
@@ -1021,7 +1019,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>319</v>
       </c>
@@ -1032,7 +1030,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>320</v>
       </c>
@@ -1043,7 +1041,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>321</v>
       </c>
@@ -1054,7 +1052,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="7" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:3" s="7" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="8" t="s">
         <v>0</v>
       </c>
@@ -1065,12 +1063,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="7" customFormat="1" ht="29.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:3" s="7" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1</v>
       </c>
@@ -1081,7 +1079,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2</v>
       </c>
@@ -1092,7 +1090,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:3" s="7" customFormat="1" ht="59.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:3" s="7" customFormat="1" ht="59.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="8" t="s">
         <v>0</v>
       </c>
@@ -1103,12 +1101,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:3" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>1</v>
       </c>
@@ -1119,7 +1117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2</v>
       </c>
@@ -1130,7 +1128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3</v>
       </c>
@@ -1141,7 +1139,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>100</v>
       </c>
@@ -1152,7 +1150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>200</v>
       </c>
@@ -1163,7 +1161,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>300</v>
       </c>
@@ -1174,7 +1172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>301</v>
       </c>
@@ -1185,7 +1183,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>302</v>
       </c>
@@ -1196,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>303</v>
       </c>
@@ -1207,7 +1205,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>304</v>
       </c>
@@ -1218,7 +1216,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>305</v>
       </c>
@@ -1229,7 +1227,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>306</v>
       </c>
@@ -1240,7 +1238,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>307</v>
       </c>
@@ -1251,7 +1249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>308</v>
       </c>
@@ -1262,7 +1260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>309</v>
       </c>
@@ -1273,7 +1271,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>310</v>
       </c>
@@ -1284,7 +1282,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>311</v>
       </c>
@@ -1295,7 +1293,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>312</v>
       </c>
@@ -1306,7 +1304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>313</v>
       </c>
@@ -1317,7 +1315,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>314</v>
       </c>
@@ -1328,12 +1326,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>315</v>
       </c>
@@ -1344,7 +1342,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>316</v>
       </c>
@@ -1355,7 +1353,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>317</v>
       </c>
@@ -1366,7 +1364,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>318</v>
       </c>
@@ -1377,7 +1375,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>319</v>
       </c>
@@ -1388,7 +1386,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>320</v>
       </c>
@@ -1399,7 +1397,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="73" spans="1:3" s="7" customFormat="1" ht="58.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:3" s="7" customFormat="1" ht="58.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="10" t="s">
         <v>0</v>
       </c>
@@ -1410,12 +1408,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:3" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" s="7" customFormat="1" ht="22.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B74" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1</v>
       </c>
@@ -1426,7 +1424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>2</v>
       </c>
@@ -1437,7 +1435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>3</v>
       </c>
@@ -1448,7 +1446,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>100</v>
       </c>
@@ -1459,7 +1457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>200</v>
       </c>
@@ -1470,7 +1468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>300</v>
       </c>
@@ -1481,7 +1479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>301</v>
       </c>
@@ -1492,7 +1490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>302</v>
       </c>
@@ -1503,7 +1501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>303</v>
       </c>
@@ -1514,7 +1512,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>304</v>
       </c>
@@ -1525,7 +1523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>305</v>
       </c>
@@ -1536,7 +1534,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>306</v>
       </c>
@@ -1547,7 +1545,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>307</v>
       </c>
@@ -1558,7 +1556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>308</v>
       </c>
@@ -1569,7 +1567,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>309</v>
       </c>
@@ -1580,7 +1578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>310</v>
       </c>
@@ -1591,7 +1589,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>311</v>
       </c>
@@ -1602,13 +1600,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>312</v>
       </c>
@@ -1619,7 +1617,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>313</v>
       </c>
@@ -1630,7 +1628,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>314</v>
       </c>
@@ -1641,7 +1639,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>315</v>
       </c>
@@ -1652,7 +1650,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>316</v>
       </c>
@@ -1663,7 +1661,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>317</v>
       </c>
@@ -1674,7 +1672,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>318</v>
       </c>
@@ -1685,7 +1683,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>319</v>
       </c>
@@ -1696,7 +1694,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>320</v>
       </c>
@@ -1707,7 +1705,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>321</v>
       </c>
@@ -1718,7 +1716,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="107" spans="1:3" s="7" customFormat="1" ht="59.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:3" s="7" customFormat="1" ht="59.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="8" t="s">
         <v>0</v>
       </c>
@@ -1729,12 +1727,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:3" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:3" s="7" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B108" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>1</v>
       </c>
@@ -1745,7 +1743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>2</v>
       </c>
@@ -1756,7 +1754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>3</v>
       </c>
@@ -1767,7 +1765,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>100</v>
       </c>
@@ -1778,7 +1776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>200</v>
       </c>
@@ -1789,7 +1787,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>300</v>
       </c>
@@ -1800,7 +1798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>301</v>
       </c>
@@ -1811,7 +1809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>302</v>
       </c>
@@ -1822,7 +1820,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>303</v>
       </c>
@@ -1833,7 +1831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>304</v>
       </c>
@@ -1844,7 +1842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>305</v>
       </c>
@@ -1855,7 +1853,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>306</v>
       </c>
@@ -1866,8 +1864,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="121" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="13">
+    <row r="121" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>307</v>
       </c>
       <c r="B121" s="3" t="s">
@@ -1877,8 +1875,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="14">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="5">
         <v>308</v>
       </c>
       <c r="B122" s="5" t="s">
@@ -1888,8 +1886,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="14">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="5">
         <v>309</v>
       </c>
       <c r="B123" s="5" t="s">
@@ -1899,8 +1897,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="14">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="5">
         <v>310</v>
       </c>
       <c r="B124" s="5" t="s">
@@ -1910,8 +1908,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="14">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="5">
         <v>311</v>
       </c>
       <c r="B125" s="5" t="s">
@@ -1921,8 +1919,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="14">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="5">
         <v>312</v>
       </c>
       <c r="B126" s="5" t="s">
@@ -1932,8 +1930,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="14">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
         <v>313</v>
       </c>
       <c r="B127" s="5" t="s">
@@ -1943,8 +1941,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="13">
+    <row r="128" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
         <v>314</v>
       </c>
       <c r="B128" s="3" t="s">
@@ -1954,8 +1952,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="14">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="5">
         <v>315</v>
       </c>
       <c r="B129" s="5" t="s">
@@ -1965,14 +1963,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="15"/>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B130" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="14">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="5">
         <v>316</v>
       </c>
       <c r="B131" s="5" t="s">
@@ -1982,8 +1979,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="14">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="5">
         <v>317</v>
       </c>
       <c r="B132" s="5" t="s">
@@ -1993,8 +1990,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="133" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="13">
+    <row r="133" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
         <v>318</v>
       </c>
       <c r="B133" s="3" t="s">
@@ -2004,8 +2001,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="14">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="5">
         <v>319</v>
       </c>
       <c r="B134" s="5" t="s">
@@ -2015,7 +2012,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>320</v>
       </c>
@@ -2026,8 +2023,8 @@
         <v>44</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="14">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="5">
         <v>321</v>
       </c>
       <c r="B136" s="5" t="s">
@@ -2037,8 +2034,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="14">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="5">
         <v>322</v>
       </c>
       <c r="B137" s="5" t="s">
@@ -2051,4 +2048,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD85799B-7BD6-4E4C-80EE-A80797FFD741}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>